--- a/etf_holdings/2026-09-30_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-09-30_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,100 +589,150 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
+          <t>00990A_異動類型</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00990A_調整方向</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>00990A_股票名稱_昨日</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>00990A_股票名稱_今日</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>00990A_權重_昨日</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>00990A_權重_今日</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>00990A_權重變化</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>00990A_股數_昨日</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>00990A_股數_今日</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>00990A_股數變化</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
           <t>00407A_異動類型</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>00407A_調整方向</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>00407A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>00407A_權重_昨日</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>00407A_權重_今日</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>00407A_權重變化</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>00407A_股數_昨日</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>00407A_股數_今日</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>00400A_異動類型</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>00400A_調整方向</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_昨日</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>00400A_股票名稱_今日</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>00400A_權重_昨日</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>00400A_權重_今日</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>00400A_權重變化</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>00400A_股數_昨日</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>00400A_股數_今日</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>00400A_股數變化</t>
         </is>
@@ -845,80 +895,90 @@
           <t>-100,000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>2.48%</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>1.90%</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>-0.58%</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AZ2" t="n">
         <v>322000</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
         <v>252000</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-70,000</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>刪除</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>全數賣出</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr">
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="n">
         <v>227000</v>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -932,11 +992,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00400A,00403A,00407A</t>
+          <t>00400A,00403A,00407A,00990A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1007,92 +1067,120 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>貿聯-KY</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="n">
+        <v>94000</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2.35%</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>3.21%</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>+0.86%</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AZ3" t="n">
         <v>226000</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="BA3" t="n">
         <v>291000</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>65,000</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>貿聯-KY</t>
         </is>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2.05%</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2.65%</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>+0.60%</t>
         </is>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BJ3" t="n">
         <v>241000</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BK3" t="n">
         <v>295000</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>54,000</t>
         </is>
@@ -1101,20 +1189,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00400A,00991A</t>
+          <t>00403A,00990A,00991A</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1124,43 +1212,43 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7000000</v>
+        <v>150000</v>
       </c>
       <c r="M4" t="n">
-        <v>8000000</v>
+        <v>1000</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>-149,000</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -1173,82 +1261,110 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3.92%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>3.51%</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
       <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.86%</t>
+        </is>
+      </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+      <c r="AP4" t="n">
+        <v>60000</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>南亞</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3.12%</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3.69%</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>+0.57%</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3627000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4167000</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>540,000</t>
-        </is>
-      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1256,7 +1372,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00403A,00991A</t>
+          <t>00400A,00991A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1266,43 +1382,43 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-1.00%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>150000</v>
+        <v>7000000</v>
       </c>
       <c r="M5" t="n">
-        <v>1000</v>
+        <v>8000000</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-149,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -1315,52 +1431,16 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3.92%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>3.51%</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>-0.41%</t>
-        </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-100,000</t>
-        </is>
-      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
@@ -1381,6 +1461,52 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>南亞</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>3.69%</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>+0.57%</t>
+        </is>
+      </c>
+      <c r="BJ5" t="n">
+        <v>3627000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4167000</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>540,000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
